--- a/code/JieLi_Home_Demo/Languages/language.xlsx
+++ b/code/JieLi_Home_Demo/Languages/language.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27100" windowHeight="16760"/>
+    <workbookView windowWidth="26160" windowHeight="16640"/>
   </bookViews>
   <sheets>
     <sheet name="语言包" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="678">
   <si>
     <t>界面</t>
   </si>
@@ -410,6 +410,15 @@
     <t>対面翻訳を終了してもよろしいですか?</t>
   </si>
   <si>
+    <t>对方正在说话...</t>
+  </si>
+  <si>
+    <t>The other party is talking...</t>
+  </si>
+  <si>
+    <t>相手が話しているのですが…</t>
+  </si>
+  <si>
     <t>请佩戴好耳机，单击下方按钮开始翻译</t>
   </si>
   <si>
@@ -419,6 +428,78 @@
     <t>ヘッドフォンを装着して、下のボタンをクリックして翻訳を開始してください。</t>
   </si>
   <si>
+    <t>需要麦克风权限</t>
+  </si>
+  <si>
+    <t>Microphone permission is required</t>
+  </si>
+  <si>
+    <t>マイクの許可が必要です</t>
+  </si>
+  <si>
+    <t>请到设置中开启麦克风权限</t>
+  </si>
+  <si>
+    <t>Please enable microphone permission in settings</t>
+  </si>
+  <si>
+    <t>設定でマイクの許可を有効にしてください</t>
+  </si>
+  <si>
+    <t>去设置</t>
+  </si>
+  <si>
+    <t>Go to settings</t>
+  </si>
+  <si>
+    <t>設定に移動</t>
+  </si>
+  <si>
+    <t>暂不支持</t>
+  </si>
+  <si>
+    <t>Not supported yet</t>
+  </si>
+  <si>
+    <t>まだサポートされていません</t>
+  </si>
+  <si>
+    <t>暂无记录</t>
+  </si>
+  <si>
+    <t>No records yet</t>
+  </si>
+  <si>
+    <t>まだ記録はありません</t>
+  </si>
+  <si>
+    <t>您是否确定退出同声传译并删除翻译记录？</t>
+  </si>
+  <si>
+    <t>Are you sure you want to exit simultaneous interpretation and delete the translation history?</t>
+  </si>
+  <si>
+    <t>同時通訳を終了して翻訳履歴を削除してもよろしいですか?</t>
+  </si>
+  <si>
+    <t>我方翻译尚未完成</t>
+  </si>
+  <si>
+    <t>Our translation is not yet completed</t>
+  </si>
+  <si>
+    <t>翻訳はまだ完了していません</t>
+  </si>
+  <si>
+    <t>处理中，请稍后重试</t>
+  </si>
+  <si>
+    <t>Busy processing, please try again later</t>
+  </si>
+  <si>
+    <t>処理中です。しばらくしてから再度お試しください。</t>
+  </si>
+  <si>
     <t>翻译记录</t>
   </si>
   <si>
@@ -429,6 +510,1557 @@
   </si>
   <si>
     <t>すべての記録</t>
+  </si>
+  <si>
+    <t>记录类型</t>
+  </si>
+  <si>
+    <t>Record Type</t>
+  </si>
+  <si>
+    <t>レコードタイプ</t>
+  </si>
+  <si>
+    <t>再生</t>
+  </si>
+  <si>
+    <t>暂停</t>
+  </si>
+  <si>
+    <t>Pause</t>
+  </si>
+  <si>
+    <t>一時停止</t>
+  </si>
+  <si>
+    <t>播放原文</t>
+  </si>
+  <si>
+    <t>Play original</t>
+  </si>
+  <si>
+    <t>オリジナルを再生</t>
+  </si>
+  <si>
+    <t>播放译文</t>
+  </si>
+  <si>
+    <t>Play translated</t>
+  </si>
+  <si>
+    <t>翻訳版を再生</t>
+  </si>
+  <si>
+    <t>播放原文中</t>
+  </si>
+  <si>
+    <t>Playing original</t>
+  </si>
+  <si>
+    <t>オリジナルを再生中</t>
+  </si>
+  <si>
+    <t>播放译文中</t>
+  </si>
+  <si>
+    <t>Playing translated</t>
+  </si>
+  <si>
+    <t>翻訳版を再生中</t>
+  </si>
+  <si>
+    <t>健康</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>运动步数</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>歩数</t>
+  </si>
+  <si>
+    <t>步</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>歩</t>
+  </si>
+  <si>
+    <t>心率</t>
+  </si>
+  <si>
+    <t>Heart Rate</t>
+  </si>
+  <si>
+    <t>心拍数</t>
+  </si>
+  <si>
+    <t>次/分</t>
+  </si>
+  <si>
+    <t>BPM</t>
+  </si>
+  <si>
+    <t>血氧饱和度</t>
+  </si>
+  <si>
+    <t>Blood Oxygen Saturation</t>
+  </si>
+  <si>
+    <t>血中酸素飽和度</t>
+  </si>
+  <si>
+    <t>开始检测</t>
+  </si>
+  <si>
+    <t>Start monitoring</t>
+  </si>
+  <si>
+    <t>モニタリングを開始</t>
+  </si>
+  <si>
+    <t>历史记录</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>履歴</t>
+  </si>
+  <si>
+    <t>心率范围</t>
+  </si>
+  <si>
+    <t>Heart rate range</t>
+  </si>
+  <si>
+    <t>心拍数範囲</t>
+  </si>
+  <si>
+    <t>本日平均</t>
+  </si>
+  <si>
+    <t>Daily average</t>
+  </si>
+  <si>
+    <t>1日平均</t>
+  </si>
+  <si>
+    <t>总步数</t>
+  </si>
+  <si>
+    <t>Total steps</t>
+  </si>
+  <si>
+    <t>総歩数</t>
+  </si>
+  <si>
+    <t>总消耗</t>
+  </si>
+  <si>
+    <t>Total calories burned</t>
+  </si>
+  <si>
+    <t>総消費カロリー</t>
+  </si>
+  <si>
+    <t>千卡</t>
+  </si>
+  <si>
+    <t>Kcal</t>
+  </si>
+  <si>
+    <t>kcal</t>
+  </si>
+  <si>
+    <t>停止计步</t>
+  </si>
+  <si>
+    <t>Stop pedometer</t>
+  </si>
+  <si>
+    <t>歩数計を停止</t>
+  </si>
+  <si>
+    <t>步数</t>
+  </si>
+  <si>
+    <t>开始计步</t>
+  </si>
+  <si>
+    <t>Start pedometer</t>
+  </si>
+  <si>
+    <t>歩数計を開始</t>
+  </si>
+  <si>
+    <t>正常 95 – 100%       偏低 90 – 94%       警告 ≤90%</t>
+  </si>
+  <si>
+    <t>Normal 95 – 100%       Low 90 – 94%       Warning ≤90%</t>
+  </si>
+  <si>
+    <t>正常 95 – 100%       低 90 – 94%       警告 ≤90%</t>
+  </si>
+  <si>
+    <t>最低值-最高值</t>
+  </si>
+  <si>
+    <t>Min-Max</t>
+  </si>
+  <si>
+    <t>最小値・最大値</t>
+  </si>
+  <si>
+    <t>心率检测</t>
+  </si>
+  <si>
+    <t>Heart rate monitoring</t>
+  </si>
+  <si>
+    <t>心拍数モニタリング</t>
+  </si>
+  <si>
+    <t>血氧检测</t>
+  </si>
+  <si>
+    <t>Blood oxygen monitoring</t>
+  </si>
+  <si>
+    <t>血中酸素モニタリング</t>
+  </si>
+  <si>
+    <t>正在检测中</t>
+  </si>
+  <si>
+    <t>Testing in progress</t>
+  </si>
+  <si>
+    <t>テスト中</t>
+  </si>
+  <si>
+    <t>请保持静止</t>
+  </si>
+  <si>
+    <t>Please remain still</t>
+  </si>
+  <si>
+    <t>動かないでください</t>
+  </si>
+  <si>
+    <t>检测完成</t>
+  </si>
+  <si>
+    <t>Testing completed</t>
+  </si>
+  <si>
+    <t>テスト完了</t>
+  </si>
+  <si>
+    <t>检测失败</t>
+  </si>
+  <si>
+    <t>Test failed</t>
+  </si>
+  <si>
+    <t>テスト失敗</t>
+  </si>
+  <si>
+    <t>1.请先确认耳机佩戴方式正确\n2.检测期间请保持静止，避免移动或说话\n3.确保耳机检测窗与耳背有效接触，无头发等异物遮挡</t>
+  </si>
+  <si>
+    <t>1. Please make sure the earphones are worn correctly.\n 2. Please remain still during the test and avoid moving or talking. \n3. Ensure that the earphone detection window is in effective contact with the back of the ear and there is no foreign matter such as hair blocking it.</t>
+  </si>
+  <si>
+    <t>1. イヤホンが正しく装着されていることを確認してください。\n2. テスト中は動かず、動いたり話したりしないでください。\n3. イヤホンの検出ウィンドウが耳の奥にしっかりと接触し、髪の毛などの異物で塞がれていないことを確認してください。</t>
+  </si>
+  <si>
+    <t>重试</t>
+  </si>
+  <si>
+    <t>Retry</t>
+  </si>
+  <si>
+    <t>再試行</t>
+  </si>
+  <si>
+    <t>步数更新频率（s）</t>
+  </si>
+  <si>
+    <t>Step count update frequency (s)</t>
+  </si>
+  <si>
+    <t>歩数更新頻度（s）</t>
+  </si>
+  <si>
+    <t>yyyy年MM月dd日 E</t>
+  </si>
+  <si>
+    <t>yMMMMdEEEE</t>
+  </si>
+  <si>
+    <t>yyyy年MM月dd日EEEE</t>
+  </si>
+  <si>
+    <t>多媒体</t>
+  </si>
+  <si>
+    <t>暂无数据，请先连接设备</t>
+  </si>
+  <si>
+    <t>No data yet, please connect the device first</t>
+  </si>
+  <si>
+    <t>データなし、有線デバイス</t>
+  </si>
+  <si>
+    <t>提示框</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>プロンプト</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>キャンセル</t>
+  </si>
+  <si>
+    <t>确定</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>打开设置</t>
+  </si>
+  <si>
+    <t>Open Settings</t>
+  </si>
+  <si>
+    <t>設定を開く</t>
+  </si>
+  <si>
+    <t>I Know</t>
+  </si>
+  <si>
+    <t>了解しました</t>
+  </si>
+  <si>
+    <t>当前尚未添加豆包模型密钥,请扫码输入密钥!!</t>
+  </si>
+  <si>
+    <t>The Doubao model key has not yet been added. Please scan the QR code to enter the key!</t>
+  </si>
+  <si>
+    <t>Doubaoのモデルキーはまだ追加されていません。QRコードをスキャンしてキーを入力してください。</t>
+  </si>
+  <si>
+    <t>密钥添加成功！</t>
+  </si>
+  <si>
+    <t>Key add success!</t>
+  </si>
+  <si>
+    <t>キーの追加に成功しました！</t>
+  </si>
+  <si>
+    <t>密钥添加失败！</t>
+  </si>
+  <si>
+    <t>Key add failed!</t>
+  </si>
+  <si>
+    <t>キーの追加に失敗しました！</t>
+  </si>
+  <si>
+    <t>输入密码框</t>
+  </si>
+  <si>
+    <t>输入密码</t>
+  </si>
+  <si>
+    <t>Enter Password</t>
+  </si>
+  <si>
+    <t>パスワードを入力してください</t>
+  </si>
+  <si>
+    <t>请输入\"%@\"的密码</t>
+  </si>
+  <si>
+    <t>Please enter the password for [%@]</t>
+  </si>
+  <si>
+    <t>パスワード「%@」を入力してください</t>
+  </si>
+  <si>
+    <t>连接</t>
+  </si>
+  <si>
+    <t>Connect</t>
+  </si>
+  <si>
+    <t>接続</t>
+  </si>
+  <si>
+    <t>请输入密码</t>
+  </si>
+  <si>
+    <t>Please enter password</t>
+  </si>
+  <si>
+    <t>请输入16字节的密码</t>
+  </si>
+  <si>
+    <t>Please enter a 16-byte password</t>
+  </si>
+  <si>
+    <t>16バイトのパスワードを入力してください</t>
+  </si>
+  <si>
+    <t>扫码连接</t>
+  </si>
+  <si>
+    <t>Scan code to connect</t>
+  </si>
+  <si>
+    <t>QR 接続</t>
+  </si>
+  <si>
+    <t>音量控制框</t>
+  </si>
+  <si>
+    <t>音量</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>左右耳音量平衡</t>
+  </si>
+  <si>
+    <t>Volume Balance</t>
+  </si>
+  <si>
+    <t>左右の耳の音量バランス</t>
+  </si>
+  <si>
+    <t>设备不支持音量控制</t>
+  </si>
+  <si>
+    <t>Device does not support volume control.</t>
+  </si>
+  <si>
+    <t>デバイスは音量調節に対応していません</t>
+  </si>
+  <si>
+    <t>输入名称框</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>请输入4-32字节的名称</t>
+  </si>
+  <si>
+    <t>Please enter a name of 4-32 characters</t>
+  </si>
+  <si>
+    <t>4～32バイトの名前を入力してください</t>
+  </si>
+  <si>
+    <t>登录验证框</t>
+  </si>
+  <si>
+    <t>登录</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>ログイン</t>
+  </si>
+  <si>
+    <t>扫码登录</t>
+  </si>
+  <si>
+    <t>Scan QR code to log in</t>
+  </si>
+  <si>
+    <t>QRコードをスキャンしてログインしてください</t>
+  </si>
+  <si>
+    <t>登录失败。</t>
+  </si>
+  <si>
+    <t>Login failed.</t>
+  </si>
+  <si>
+    <t>ログインに失敗しました。</t>
+  </si>
+  <si>
+    <t>请输入至少6个字符的密码</t>
+  </si>
+  <si>
+    <t>Please enter a password of at least 6 characters</t>
+  </si>
+  <si>
+    <t>6文字以上のパスワードを入力してください</t>
+  </si>
+  <si>
+    <t>错误密码</t>
+  </si>
+  <si>
+    <t>Wrong Password</t>
+  </si>
+  <si>
+    <t>パスワードが間違っています</t>
+  </si>
+  <si>
+    <t>Scan to connect</t>
+  </si>
+  <si>
+    <t>スキャンして接続してください</t>
+  </si>
+  <si>
+    <t>自动登录成功</t>
+  </si>
+  <si>
+    <t>Automatic login successful.</t>
+  </si>
+  <si>
+    <t>自動ログインに成功しました。</t>
+  </si>
+  <si>
+    <t>主页</t>
+  </si>
+  <si>
+    <t>设备</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>デバイス</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>設定</t>
+  </si>
+  <si>
+    <t>我的设备</t>
+  </si>
+  <si>
+    <t>My Devices</t>
+  </si>
+  <si>
+    <t>マイデバイス</t>
+  </si>
+  <si>
+    <t>可连接设备</t>
+  </si>
+  <si>
+    <t>Connectable Devices</t>
+  </si>
+  <si>
+    <t>接続可能なデバイス</t>
+  </si>
+  <si>
+    <t>检测到手机蓝牙未开启\n是否打开设置开启？</t>
+  </si>
+  <si>
+    <t>It is detected that the Bluetooth of the mobile phone is not turned on. \nDo you want to turn it on?</t>
+  </si>
+  <si>
+    <t>携帯電話のBluetoothがオンになっていないことが検出されました。\nオンにしますか？</t>
+  </si>
+  <si>
+    <t>检测到位置服务未开启\n是否打开设置开启？</t>
+  </si>
+  <si>
+    <t>It is detected that the location service is not turned on. \nDo you want to turn it on?</t>
+  </si>
+  <si>
+    <t>位置情報サービスがオンになっていないことが検出されました。\nオンにしますか？</t>
+  </si>
+  <si>
+    <t>未检索到设备</t>
+  </si>
+  <si>
+    <t>Device Not Found</t>
+  </si>
+  <si>
+    <t>デバイスが見つかりません</t>
+  </si>
+  <si>
+    <t>请检查设备已打开，点击下方按钮后再试</t>
+  </si>
+  <si>
+    <t>Please check that your device is turned on and click the button below to try again</t>
+  </si>
+  <si>
+    <t>デバイスの電源がオンになっていることを確認し、下のボタンをクリックしてもう一度お試しください</t>
+  </si>
+  <si>
+    <t>打开蓝牙搜索失败</t>
+  </si>
+  <si>
+    <t>Failed to search device</t>
+  </si>
+  <si>
+    <t>デバイスの検索に失敗しました</t>
+  </si>
+  <si>
+    <t>请检查手机蓝牙是否可用</t>
+  </si>
+  <si>
+    <t>Please check whether the Bluetooth of your mobile phone is available</t>
+  </si>
+  <si>
+    <t>携帯電話のBluetoothが利用可能かどうかを確認してください</t>
+  </si>
+  <si>
+    <t>蓝牙未打开</t>
+  </si>
+  <si>
+    <t>Bluetooth is close</t>
+  </si>
+  <si>
+    <t>Bluetoothがオンになっています</t>
+  </si>
+  <si>
+    <t>位置服务未打开</t>
+  </si>
+  <si>
+    <t>Location services is close</t>
+  </si>
+  <si>
+    <t>位置情報サービスがオフになっています</t>
+  </si>
+  <si>
+    <t>搜索蓝牙设备需要用户允许使用手机位置服务</t>
+  </si>
+  <si>
+    <t>Searching for Bluetooth devices requires user permission to use the phone\'s location service</t>
+  </si>
+  <si>
+    <t>Bluetoothデバイスを検索するには、携帯電話の位置情報サービスを使用するためのユーザー許可が必要です</t>
+  </si>
+  <si>
+    <t>缺少权限</t>
+  </si>
+  <si>
+    <t>Missing Permissions</t>
+  </si>
+  <si>
+    <t>権限がありません</t>
+  </si>
+  <si>
+    <t>请到[应用管理]-&gt;[权限管理]允许权限</t>
+  </si>
+  <si>
+    <t>Please go to [Application Management]-&gt;[Permission Management] to allow permissions</t>
+  </si>
+  <si>
+    <t>[アプリケーション管理] -&gt; [権限管理] に移動して権限を許可してください</t>
+  </si>
+  <si>
+    <t>搜索设备失败</t>
+  </si>
+  <si>
+    <t>重新搜索</t>
+  </si>
+  <si>
+    <t>Search Again</t>
+  </si>
+  <si>
+    <t>再度検索</t>
+  </si>
+  <si>
+    <t>正在连接设备，请稍等</t>
+  </si>
+  <si>
+    <t>Connecting to device, please wait</t>
+  </si>
+  <si>
+    <t>デバイスに接続しています。お待ちください</t>
+  </si>
+  <si>
+    <t>是否断开与设备(%@)的连接？</t>
+  </si>
+  <si>
+    <t>Do you want to disconnect from the device(%@)?</t>
+  </si>
+  <si>
+    <t>デバイス(%@)から切断しますか？</t>
+  </si>
+  <si>
+    <t>%@'\n密码不正确</t>
+  </si>
+  <si>
+    <t>[%@]\nIncorrect Password</t>
+  </si>
+  <si>
+    <t>%@\nパスワードが正しくありません</t>
+  </si>
+  <si>
+    <t>%@'\n同步超时</t>
+  </si>
+  <si>
+    <t>[%@]\nSynchronization Timeout</t>
+  </si>
+  <si>
+    <t>%@\n同期タイムアウト</t>
+  </si>
+  <si>
+    <t>%@'\n同步失败</t>
+  </si>
+  <si>
+    <t>[%@]\nSynchronization Failed</t>
+  </si>
+  <si>
+    <t>%@\n同期に失敗しました</t>
+  </si>
+  <si>
+    <t>搜索蓝牙设备需要用户允许使用位置服务</t>
+  </si>
+  <si>
+    <t>Searching for Bluetooth devices requires user permission to use location services</t>
+  </si>
+  <si>
+    <t>Bluetoothデバイスを検索するには、位置情報サービスを使用するためのユーザーの許可が必要です</t>
+  </si>
+  <si>
+    <t>搜索或者连接蓝牙设备需要用户允许访问附近的设备</t>
+  </si>
+  <si>
+    <t>Searching or connecting to Bluetooth devices requires user permission to access nearby devices</t>
+  </si>
+  <si>
+    <t>Bluetoothデバイスを検索または接続するには、近くのデバイスにアクセスするためのユーザーの許可が必要です</t>
+  </si>
+  <si>
+    <t>请保证当前手机使用的经典蓝牙为对应的设备经典蓝牙</t>
+  </si>
+  <si>
+    <t>Please ensure that the classic Bluetooth used by the current mobile phone is the corresponding device classic Bluetooth</t>
+  </si>
+  <si>
+    <t>現在使用している携帯電話で使用されているクラシックBluetoothが、対応するデバイスのクラシックBluetoothであることを確認してください</t>
+  </si>
+  <si>
+    <t>设备[%@]已连接</t>
+  </si>
+  <si>
+    <t>Device[%@] is connected</t>
+  </si>
+  <si>
+    <t>デバイス[%@]が接続されています</t>
+  </si>
+  <si>
+    <t>未能通过 GATT 服务发现设备</t>
+  </si>
+  <si>
+    <t>Failed to discover device via GATT service</t>
+  </si>
+  <si>
+    <t>GATTサービス経由でデバイスを検出できませんでした</t>
+  </si>
+  <si>
+    <t>此设备为GATT over EDR 连接设备，需要到后台先进行连接设备经典蓝牙</t>
+  </si>
+  <si>
+    <t>This device is a GATT over EDR connection device; you need to connect the device via classic Bluetooth in the background first.</t>
+  </si>
+  <si>
+    <t>このデバイスは GATT over EDR 接続デバイスです。まずバックグラウンドでクラシック Bluetooth 経由でデバイスに接続する必要があります。</t>
+  </si>
+  <si>
+    <t>未连上设备的经典蓝牙</t>
+  </si>
+  <si>
+    <t>The device's classic Bluetooth is not connected</t>
+  </si>
+  <si>
+    <t>デバイスのクラシックBluetoothは接続されていません</t>
+  </si>
+  <si>
+    <t>删除设备</t>
+  </si>
+  <si>
+    <t>删除此设备</t>
+  </si>
+  <si>
+    <t>Delete Device</t>
+  </si>
+  <si>
+    <t>デバイスの削除</t>
+  </si>
+  <si>
+    <t>正在删除</t>
+  </si>
+  <si>
+    <t>Deleting...</t>
+  </si>
+  <si>
+    <t>削除中...</t>
+  </si>
+  <si>
+    <t>删除设备失败。\n错误码: %d,%@</t>
+  </si>
+  <si>
+    <t>Failed to delete the device.\nError code:  %d,%@</t>
+  </si>
+  <si>
+    <t>デバイスの削除に失敗しました。\nエラーコード:  %d,%@</t>
+  </si>
+  <si>
+    <t>Auracast(接收端)</t>
+  </si>
+  <si>
+    <t>收听Auracast广播</t>
+  </si>
+  <si>
+    <t>Listen Auracast Broadcast</t>
+  </si>
+  <si>
+    <t>Auracast放送を聴く</t>
+  </si>
+  <si>
+    <t>Auracast</t>
+  </si>
+  <si>
+    <t>我的Auracast广播</t>
+  </si>
+  <si>
+    <t>My Auracast broadcast</t>
+  </si>
+  <si>
+    <t>私のAuracast放送</t>
+  </si>
+  <si>
+    <t>附近可用的Auracast广播</t>
+  </si>
+  <si>
+    <t>Auracast broadcasts available nearby</t>
+  </si>
+  <si>
+    <t>近くで視聴可能なAuracast放送</t>
+  </si>
+  <si>
+    <t>离开</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>終了</t>
+  </si>
+  <si>
+    <t>正在同步</t>
+  </si>
+  <si>
+    <t>Syncing...</t>
+  </si>
+  <si>
+    <t>同期中...</t>
+  </si>
+  <si>
+    <t>移除</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>请扫描正确的二维码</t>
+  </si>
+  <si>
+    <t>Please scan the correct QR code</t>
+  </si>
+  <si>
+    <t>正しいQRコードをスキャンしてください</t>
+  </si>
+  <si>
+    <t>请先打开Auracast开关</t>
+  </si>
+  <si>
+    <t>Please turn on the Auracast switch first</t>
+  </si>
+  <si>
+    <t>まずAuracastスイッチをオンにしてください</t>
+  </si>
+  <si>
+    <t>收听广播失败</t>
+  </si>
+  <si>
+    <t>Failed to receive broadcast</t>
+  </si>
+  <si>
+    <t>放送を受信できませんでした</t>
+  </si>
+  <si>
+    <t>请确保 %@ 已打开而且在通信范围内。</t>
+  </si>
+  <si>
+    <t>Please make sure '%@' is open and within communication range.</t>
+  </si>
+  <si>
+    <t>「%@」が開いており、通信範囲内にあることを確認してください。</t>
+  </si>
+  <si>
+    <t>广播搜索失败</t>
+  </si>
+  <si>
+    <t>Broadcast search failed</t>
+  </si>
+  <si>
+    <t>ブロードキャスト検索に失敗しました</t>
+  </si>
+  <si>
+    <t>扫描二维码</t>
+  </si>
+  <si>
+    <t>Scan QR code</t>
+  </si>
+  <si>
+    <t>QRコードをスキャン</t>
+  </si>
+  <si>
+    <t>扫描二维码功能需要用户允许使用摄像头权限</t>
+  </si>
+  <si>
+    <t>The QR code scanning function requires the user to allow the use of the camera permission</t>
+  </si>
+  <si>
+    <t>QRコードスキャン機能を使用するには、カメラの使用許可が必要です。</t>
+  </si>
+  <si>
+    <t>扫描二维码需要使用摄像头功能，是否前往设置？</t>
+  </si>
+  <si>
+    <t>Scanning the QR code requires the use of the camera function. \nDo you want to go to settings?</t>
+  </si>
+  <si>
+    <t>QRコードをスキャンするには、カメラ機能を使用する必要があります。\n設定に移動しますか？</t>
+  </si>
+  <si>
+    <t>选择图片功能需要用户允许访问手机存储</t>
+  </si>
+  <si>
+    <t>The picture selection function requires the user to allow access to the phone storage</t>
+  </si>
+  <si>
+    <t>画像選択機能を使用するには、携帯電話のストレージへのアクセスを許可する必要があります。</t>
+  </si>
+  <si>
+    <t>选择图像功能需要访问手机存储，是否前往设置？</t>
+  </si>
+  <si>
+    <t>Selecting the image function requires access to the phone storage. \nDo you want to go to settings?</t>
+  </si>
+  <si>
+    <t>画像機能を選択するには、携帯電話のストレージへのアクセスが必要です。\n設定に移動しますか？</t>
+  </si>
+  <si>
+    <t>解析失败</t>
+  </si>
+  <si>
+    <t>Parsing Failed</t>
+  </si>
+  <si>
+    <t>解析に失敗しました</t>
+  </si>
+  <si>
+    <t>发射器设置</t>
+  </si>
+  <si>
+    <t>设备设置</t>
+  </si>
+  <si>
+    <t>Device Settings</t>
+  </si>
+  <si>
+    <t>デバイス設定</t>
+  </si>
+  <si>
+    <t>配置Auracast广播</t>
+  </si>
+  <si>
+    <t>Configure Auracast broadcast</t>
+  </si>
+  <si>
+    <t>Auracast 設定</t>
+  </si>
+  <si>
+    <t>Broadcast Name</t>
+  </si>
+  <si>
+    <t>ブロードキャスト名</t>
+  </si>
+  <si>
+    <t>发射功率</t>
+  </si>
+  <si>
+    <t>Transmit Power</t>
+  </si>
+  <si>
+    <t>送信出力</t>
+  </si>
+  <si>
+    <t>基础配置</t>
+  </si>
+  <si>
+    <t>Basic Settings</t>
+  </si>
+  <si>
+    <t>基本設定</t>
+  </si>
+  <si>
+    <t>广播配置</t>
+  </si>
+  <si>
+    <t>Broadcast Configuration</t>
+  </si>
+  <si>
+    <t>ブロードキャスト設定</t>
+  </si>
+  <si>
+    <t>密钥开关</t>
+  </si>
+  <si>
+    <t>Encryption Settings</t>
+  </si>
+  <si>
+    <t>暗号化設定</t>
+  </si>
+  <si>
+    <t>密钥设置</t>
+  </si>
+  <si>
+    <t>Broadcast Code</t>
+  </si>
+  <si>
+    <t>ブロードキャストコード</t>
+  </si>
+  <si>
+    <t>音频格式</t>
+  </si>
+  <si>
+    <t>Audio Format</t>
+  </si>
+  <si>
+    <t>音声フォーマット</t>
+  </si>
+  <si>
+    <t>更多设置</t>
+  </si>
+  <si>
+    <t>More Settings</t>
+  </si>
+  <si>
+    <t>詳細設定</t>
+  </si>
+  <si>
+    <t>安全设置</t>
+  </si>
+  <si>
+    <t>Security Settings</t>
+  </si>
+  <si>
+    <t>セキュリティ設定</t>
+  </si>
+  <si>
+    <t>密码</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>パスワード</t>
+  </si>
+  <si>
+    <t>配置已被修改，需要重启设备生效</t>
+  </si>
+  <si>
+    <t>The configuration has been modified and the device needs to be restarted for it to take effect.</t>
+  </si>
+  <si>
+    <t>設定が変更されました。変更を有効にするには、デバイスを再起動する必要があります。</t>
+  </si>
+  <si>
+    <t>广播密钥设置</t>
+  </si>
+  <si>
+    <t>请设置密钥</t>
+  </si>
+  <si>
+    <t>Please set Broadcast Code</t>
+  </si>
+  <si>
+    <t>ブロードキャストコードを設定してください</t>
+  </si>
+  <si>
+    <t>修改</t>
+  </si>
+  <si>
+    <t>Modify</t>
+  </si>
+  <si>
+    <t>変更</t>
+  </si>
+  <si>
+    <t>生成二维码</t>
+  </si>
+  <si>
+    <t>Generate QR code</t>
+  </si>
+  <si>
+    <t>QRコードを生成</t>
+  </si>
+  <si>
+    <t>设置密钥成功</t>
+  </si>
+  <si>
+    <t>Set broadcast code successfully</t>
+  </si>
+  <si>
+    <t>ブロードキャストコードの設定に成功しました</t>
+  </si>
+  <si>
+    <t>音频格式设置</t>
+  </si>
+  <si>
+    <t>采样率(HZ)</t>
+  </si>
+  <si>
+    <t>Sample Rate(HZ)</t>
+  </si>
+  <si>
+    <t>サンプルレート(Hz)</t>
+  </si>
+  <si>
+    <t>帧间隔(微秒)</t>
+  </si>
+  <si>
+    <t>SDU Interval(us)</t>
+  </si>
+  <si>
+    <t>SDU間隔(μs)</t>
+  </si>
+  <si>
+    <t>包长度(字节)</t>
+  </si>
+  <si>
+    <t>Max SDU(Octets)</t>
+  </si>
+  <si>
+    <t>最大SDU(オクテット)</t>
+  </si>
+  <si>
+    <t>码率(kb/s)</t>
+  </si>
+  <si>
+    <t>Code Rate(kbps)</t>
+  </si>
+  <si>
+    <t>コードレート(kbps)</t>
+  </si>
+  <si>
+    <t>重发次数</t>
+  </si>
+  <si>
+    <t>RTN</t>
+  </si>
+  <si>
+    <t>最大传输延时(毫秒)</t>
+  </si>
+  <si>
+    <t>Max Transport Latency(ms)</t>
+  </si>
+  <si>
+    <t>最大トランスポート遅延(ms)</t>
+  </si>
+  <si>
+    <t>演示延时(毫秒)</t>
+  </si>
+  <si>
+    <t>Presentation Delay(ms)</t>
+  </si>
+  <si>
+    <t>プレゼンテーション遅延(ms)</t>
+  </si>
+  <si>
+    <t>保存二维码框</t>
+  </si>
+  <si>
+    <t>保存图片</t>
+  </si>
+  <si>
+    <t>Save Image</t>
+  </si>
+  <si>
+    <t>画像を保存</t>
+  </si>
+  <si>
+    <t>扫描Auracast二维码，将您的音频产品连接到此设备</t>
+  </si>
+  <si>
+    <t>Scan the Auracast QR code to connect your audio product to this device.</t>
+  </si>
+  <si>
+    <t>Auracast QRコードをスキャンして、オーディオ製品をこのデバイスに接続してください。</t>
+  </si>
+  <si>
+    <t>加载二维码失败</t>
+  </si>
+  <si>
+    <t>Failed to load QR code</t>
+  </si>
+  <si>
+    <t>QRコードの読み込みに失敗しました</t>
+  </si>
+  <si>
+    <t>保存图片失败</t>
+  </si>
+  <si>
+    <t>Failed to save image</t>
+  </si>
+  <si>
+    <t>画像を保存できませんでした</t>
+  </si>
+  <si>
+    <t>图片已保存</t>
+  </si>
+  <si>
+    <t>Image Saved</t>
+  </si>
+  <si>
+    <t>画像を保存しました</t>
+  </si>
+  <si>
+    <t>保存图片功能需要用户允许写文件权限</t>
+  </si>
+  <si>
+    <t>The save image function requires the user to allow write file permissions.</t>
+  </si>
+  <si>
+    <t>画像を保存するには、ユーザーにファイルの書き込み権限を許可する必要があります。</t>
+  </si>
+  <si>
+    <t>未加密</t>
+  </si>
+  <si>
+    <t>Unencrypted</t>
+  </si>
+  <si>
+    <t>暗号化されていません</t>
+  </si>
+  <si>
+    <t>请保存二维码，方便您的接收设备收听到此设备的音频</t>
+  </si>
+  <si>
+    <t>Please save the QR code for your receiving device to listen to the audio from this device</t>
+  </si>
+  <si>
+    <t>このデバイスからのオーディオを受信デバイスで聴くには、QRコードを保存してください。</t>
+  </si>
+  <si>
+    <t>修改登录密码</t>
+  </si>
+  <si>
+    <t>修改密码成功</t>
+  </si>
+  <si>
+    <t>Password changed successfully</t>
+  </si>
+  <si>
+    <t>パスワードが正常に変更されました</t>
+  </si>
+  <si>
+    <t>登录密码已修改，需要重启设备生效。</t>
+  </si>
+  <si>
+    <t>The login password has been changed and the device needs to be restarted for it to take effect.</t>
+  </si>
+  <si>
+    <t>ログインパスワードが変更されました。変更を有効にするには、デバイスを再起動する必要があります。</t>
+  </si>
+  <si>
+    <t>音源语言</t>
+  </si>
+  <si>
+    <t>韩语</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>韓国語</t>
+  </si>
+  <si>
+    <t>俄语</t>
+  </si>
+  <si>
+    <t>Russian</t>
+  </si>
+  <si>
+    <t>ロシア語</t>
+  </si>
+  <si>
+    <t>意大利语</t>
+  </si>
+  <si>
+    <t>Italian</t>
+  </si>
+  <si>
+    <t>イタリア語</t>
+  </si>
+  <si>
+    <t>法语</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>フランス語</t>
+  </si>
+  <si>
+    <t>德语</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>ドイツ語</t>
+  </si>
+  <si>
+    <t>泰语</t>
+  </si>
+  <si>
+    <t>Thai</t>
+  </si>
+  <si>
+    <t>タイ語</t>
+  </si>
+  <si>
+    <t>越南语</t>
+  </si>
+  <si>
+    <t>Vietnamese</t>
+  </si>
+  <si>
+    <t>ベトナム語</t>
+  </si>
+  <si>
+    <t>西班牙语</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>スペイン語</t>
+  </si>
+  <si>
+    <t>葡萄牙语</t>
+  </si>
+  <si>
+    <t>Portuguese</t>
+  </si>
+  <si>
+    <t>ポルトガル語</t>
+  </si>
+  <si>
+    <t>阿拉伯语</t>
+  </si>
+  <si>
+    <t>Arabic</t>
+  </si>
+  <si>
+    <t>アラビア語</t>
+  </si>
+  <si>
+    <t>荷兰语</t>
+  </si>
+  <si>
+    <t>Dutch</t>
+  </si>
+  <si>
+    <t>オランダ語</t>
+  </si>
+  <si>
+    <t>印度尼西亚语</t>
+  </si>
+  <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
+    <t>インドネシア語</t>
+  </si>
+  <si>
+    <t>马来语</t>
+  </si>
+  <si>
+    <t>Malay</t>
+  </si>
+  <si>
+    <t>マレー語</t>
+  </si>
+  <si>
+    <t>瑞典语</t>
+  </si>
+  <si>
+    <t>Swedish</t>
+  </si>
+  <si>
+    <t>スウェーデン語</t>
+  </si>
+  <si>
+    <t>芬兰语</t>
+  </si>
+  <si>
+    <t>Finnish</t>
+  </si>
+  <si>
+    <t>フィンランド語</t>
+  </si>
+  <si>
+    <t>土耳其语</t>
+  </si>
+  <si>
+    <t>Turkish</t>
+  </si>
+  <si>
+    <t>トルコ語</t>
+  </si>
+  <si>
+    <t>希腊语</t>
+  </si>
+  <si>
+    <t>Greek</t>
+  </si>
+  <si>
+    <t>ギリシャ語</t>
+  </si>
+  <si>
+    <t>波兰语</t>
+  </si>
+  <si>
+    <t>Polish</t>
+  </si>
+  <si>
+    <t>ポーランド語</t>
+  </si>
+  <si>
+    <t>捷克语</t>
+  </si>
+  <si>
+    <t>Czech</t>
+  </si>
+  <si>
+    <t>チェコ語</t>
+  </si>
+  <si>
+    <t>匈牙利语</t>
+  </si>
+  <si>
+    <t>Hungarian</t>
+  </si>
+  <si>
+    <t>ハンガリー語</t>
+  </si>
+  <si>
+    <t>挪威语</t>
+  </si>
+  <si>
+    <t>Norwegian</t>
+  </si>
+  <si>
+    <t>ノルウェー語</t>
+  </si>
+  <si>
+    <t>丹麦语</t>
+  </si>
+  <si>
+    <t>Danish</t>
+  </si>
+  <si>
+    <t>デンマーク語</t>
+  </si>
+  <si>
+    <t>冰岛语</t>
+  </si>
+  <si>
+    <t>Icelandic</t>
+  </si>
+  <si>
+    <t>アイスランド語</t>
+  </si>
+  <si>
+    <t>阿尔巴尼亚语</t>
+  </si>
+  <si>
+    <t>Albanian</t>
+  </si>
+  <si>
+    <t>アルバニア語</t>
+  </si>
+  <si>
+    <t>斯瓦希里语</t>
+  </si>
+  <si>
+    <t>Swahili</t>
+  </si>
+  <si>
+    <t>スワヒリ語</t>
+  </si>
+  <si>
+    <t>希伯来语</t>
+  </si>
+  <si>
+    <t>Hebrew</t>
+  </si>
+  <si>
+    <t>ヘブライ語</t>
+  </si>
+  <si>
+    <t>乌尔都语</t>
+  </si>
+  <si>
+    <t>Urdu</t>
+  </si>
+  <si>
+    <t>ウルドゥー語</t>
   </si>
 </sst>
 </file>
@@ -441,7 +2073,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,6 +2102,36 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -816,7 +2478,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -836,6 +2498,132 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -957,137 +2745,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1106,14 +2894,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1640,10 +3497,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D252"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="9.23076923076923" style="2"/>
+    <col min="1" max="1" width="26.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="40.0576923076923" style="2" customWidth="1"/>
     <col min="3" max="3" width="51.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.7115384615385" style="2" customWidth="1"/>
@@ -1872,340 +3729,2740 @@
     </row>
     <row r="19" ht="17" spans="1:4">
       <c r="A19" s="4"/>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:4">
       <c r="A20" s="4"/>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="21" ht="185" spans="1:4">
       <c r="A21" s="4"/>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:4">
       <c r="A22" s="4"/>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="23" ht="17" spans="1:4">
       <c r="A23" s="4"/>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="24" ht="34" spans="1:4">
       <c r="A24" s="4"/>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="25" ht="17" spans="1:4">
       <c r="A25" s="4"/>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="26" ht="17" spans="1:4">
       <c r="A26" s="4"/>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="27" ht="17" spans="1:4">
       <c r="A27" s="4"/>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" ht="17" spans="1:4">
       <c r="A28" s="4"/>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="29" ht="17" spans="1:4">
       <c r="A29" s="4"/>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="30" ht="51" spans="1:4">
       <c r="A30" s="4"/>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="31" ht="17" spans="1:4">
       <c r="A31" s="4"/>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" ht="17" spans="1:4">
       <c r="A32" s="4"/>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" ht="17" spans="1:4">
       <c r="A33" s="4"/>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="34" ht="17" spans="1:4">
       <c r="A34" s="4"/>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="5" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="35" ht="17" spans="1:4">
       <c r="A35" s="4"/>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="36" ht="17" spans="1:4">
       <c r="A36" s="4"/>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="5" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="37" ht="17" spans="1:4">
       <c r="A37" s="4"/>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="38" ht="17" spans="1:4">
       <c r="A38" s="4"/>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="39" ht="34" spans="1:4">
       <c r="A39" s="4"/>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="40" ht="34" spans="1:4">
       <c r="A40" s="4"/>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="41" ht="34" spans="1:4">
       <c r="A41" s="4"/>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="5" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="42" ht="34" spans="1:4">
       <c r="A42" s="4"/>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="43" ht="68" spans="1:4">
+    <row r="43" ht="34" spans="1:4">
       <c r="A43" s="4"/>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" ht="68" spans="1:4">
       <c r="A44" s="4"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" ht="17" spans="1:4">
-      <c r="A45" s="8" t="s">
+      <c r="B44" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D45" s="6" t="s">
+    </row>
+    <row r="45" ht="34" spans="1:4">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="8"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="8"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+      <c r="C45" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" ht="34" spans="1:4">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" ht="17" spans="1:4">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" ht="34" spans="1:4">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" ht="17" spans="1:4">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" ht="51" spans="1:4">
+      <c r="A50" s="4"/>
+      <c r="B50" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" ht="34" spans="1:4">
+      <c r="A51" s="4"/>
+      <c r="B51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" ht="51" spans="1:4">
+      <c r="A52" s="4"/>
+      <c r="B52" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" ht="17" spans="1:4">
+      <c r="A54" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" ht="17" spans="1:4">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="56" ht="17" spans="1:4">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" ht="17" spans="1:4">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" ht="17" spans="1:4">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" ht="17" spans="1:4">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" ht="17" spans="1:4">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" ht="17" spans="1:4">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" ht="17" spans="1:4">
+      <c r="A63" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" ht="17" spans="1:4">
+      <c r="A64" s="9"/>
+      <c r="B64" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" ht="17" spans="1:4">
+      <c r="A65" s="9"/>
+      <c r="B65" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" ht="17" spans="1:4">
+      <c r="A66" s="9"/>
+      <c r="B66" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="67" ht="17" spans="1:4">
+      <c r="A67" s="9"/>
+      <c r="B67" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" ht="17" spans="1:4">
+      <c r="A68" s="9"/>
+      <c r="B68" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="69" ht="17" spans="1:4">
+      <c r="A69" s="9"/>
+      <c r="B69" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" ht="17" spans="1:4">
+      <c r="A70" s="9"/>
+      <c r="B70" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" ht="17" spans="1:4">
+      <c r="A71" s="9"/>
+      <c r="B71" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" ht="17" spans="1:4">
+      <c r="A72" s="9"/>
+      <c r="B72" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73" ht="17" spans="1:4">
+      <c r="A73" s="9"/>
+      <c r="B73" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" ht="17" spans="1:4">
+      <c r="A74" s="9"/>
+      <c r="B74" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" ht="17" spans="1:4">
+      <c r="A75" s="9"/>
+      <c r="B75" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76" ht="17" spans="1:4">
+      <c r="A76" s="9"/>
+      <c r="B76" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="77" ht="17" spans="1:4">
+      <c r="A77" s="9"/>
+      <c r="B77" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" ht="17" spans="1:4">
+      <c r="A78" s="9"/>
+      <c r="B78" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="79" ht="51" spans="1:4">
+      <c r="A79" s="9"/>
+      <c r="B79" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="80" ht="17" spans="1:4">
+      <c r="A80" s="9"/>
+      <c r="B80" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="81" ht="17" spans="1:4">
+      <c r="A81" s="9"/>
+      <c r="B81" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="82" ht="17" spans="1:4">
+      <c r="A82" s="9"/>
+      <c r="B82" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="83" ht="17" spans="1:4">
+      <c r="A83" s="9"/>
+      <c r="B83" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="84" ht="17" spans="1:4">
+      <c r="A84" s="9"/>
+      <c r="B84" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="85" ht="17" spans="1:4">
+      <c r="A85" s="9"/>
+      <c r="B85" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="86" ht="17" spans="1:4">
+      <c r="A86" s="9"/>
+      <c r="B86" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="87" ht="202" spans="1:4">
+      <c r="A87" s="9"/>
+      <c r="B87" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="88" ht="17" spans="1:4">
+      <c r="A88" s="9"/>
+      <c r="B88" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="89" ht="17" spans="1:4">
+      <c r="A89" s="9"/>
+      <c r="B89" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" ht="17" spans="1:4">
+      <c r="A90" s="9"/>
+      <c r="B90" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="10"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+    </row>
+    <row r="92" ht="34" spans="1:4">
+      <c r="A92" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="10"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+    </row>
+    <row r="94" ht="17" spans="1:4">
+      <c r="A94" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="95" ht="17" spans="1:4">
+      <c r="A95" s="14"/>
+      <c r="B95" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="96" ht="17" spans="1:4">
+      <c r="A96" s="14"/>
+      <c r="B96" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="97" ht="17" spans="1:4">
+      <c r="A97" s="14"/>
+      <c r="B97" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="98" ht="17" spans="1:4">
+      <c r="A98" s="14"/>
+      <c r="B98" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="99" ht="84" spans="1:4">
+      <c r="A99" s="14"/>
+      <c r="B99" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="100" ht="34" spans="1:4">
+      <c r="A100" s="14"/>
+      <c r="B100" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="101" ht="34" spans="1:4">
+      <c r="A101" s="14"/>
+      <c r="B101" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="15"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="5"/>
+    </row>
+    <row r="103" ht="34" spans="1:4">
+      <c r="A103" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="104" ht="34" spans="1:4">
+      <c r="A104" s="14"/>
+      <c r="B104" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="105" ht="17" spans="1:4">
+      <c r="A105" s="14"/>
+      <c r="B105" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="106" ht="34" spans="1:4">
+      <c r="A106" s="14"/>
+      <c r="B106" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="107" ht="34" spans="1:4">
+      <c r="A107" s="14"/>
+      <c r="B107" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="108" ht="17" spans="1:4">
+      <c r="A108" s="14"/>
+      <c r="B108" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="C108" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="14"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="20"/>
+    </row>
+    <row r="110" ht="17" spans="1:4">
+      <c r="A110" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="111" ht="34" spans="1:4">
+      <c r="A111" s="14"/>
+      <c r="B111" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="112" ht="34" spans="1:4">
+      <c r="A112" s="14"/>
+      <c r="B112" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="14"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="21"/>
+      <c r="D113" s="5"/>
+    </row>
+    <row r="114" ht="17" spans="1:4">
+      <c r="A114" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="115" ht="34" spans="1:4">
+      <c r="A115" s="22"/>
+      <c r="B115" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C115" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="22"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="21"/>
+      <c r="D116" s="5"/>
+    </row>
+    <row r="117" ht="17" spans="1:4">
+      <c r="A117" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C117" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="118" ht="51" spans="1:4">
+      <c r="A118" s="22"/>
+      <c r="B118" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C118" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="119" ht="34" spans="1:4">
+      <c r="A119" s="22"/>
+      <c r="B119" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C119" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="120" ht="34" spans="1:4">
+      <c r="A120" s="22"/>
+      <c r="B120" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="121" ht="34" spans="1:4">
+      <c r="A121" s="22"/>
+      <c r="B121" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C121" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="122" ht="34" spans="1:4">
+      <c r="A122" s="22"/>
+      <c r="B122" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="123" ht="34" spans="1:4">
+      <c r="A123" s="22"/>
+      <c r="B123" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="C123" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="22"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="21"/>
+      <c r="D124" s="5"/>
+    </row>
+    <row r="125" ht="17" spans="1:4">
+      <c r="A125" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C125" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="126" ht="17" spans="1:4">
+      <c r="A126" s="14"/>
+      <c r="B126" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C126" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="14"/>
+      <c r="B127" s="12"/>
+      <c r="C127" s="21"/>
+      <c r="D127" s="5"/>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="14"/>
+      <c r="B128" s="12"/>
+      <c r="C128" s="21"/>
+      <c r="D128" s="5"/>
+    </row>
+    <row r="129" ht="17" spans="1:4">
+      <c r="A129" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C129" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="130" ht="17" spans="1:4">
+      <c r="A130" s="14"/>
+      <c r="B130" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="131" ht="68" spans="1:4">
+      <c r="A131" s="14"/>
+      <c r="B131" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C131" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="132" ht="68" spans="1:4">
+      <c r="A132" s="14"/>
+      <c r="B132" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="133" ht="34" spans="1:4">
+      <c r="A133" s="14"/>
+      <c r="B133" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C133" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="134" ht="84" spans="1:4">
+      <c r="A134" s="14"/>
+      <c r="B134" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C134" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="135" ht="34" spans="1:4">
+      <c r="A135" s="14"/>
+      <c r="B135" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C135" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="136" ht="51" spans="1:4">
+      <c r="A136" s="14"/>
+      <c r="B136" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C136" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="137" ht="34" spans="1:4">
+      <c r="A137" s="14"/>
+      <c r="B137" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C137" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="138" ht="34" spans="1:4">
+      <c r="A138" s="14"/>
+      <c r="B138" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="C138" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="139" ht="84" spans="1:4">
+      <c r="A139" s="14"/>
+      <c r="B139" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C139" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="140" ht="17" spans="1:4">
+      <c r="A140" s="14"/>
+      <c r="B140" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C140" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="141" ht="68" spans="1:4">
+      <c r="A141" s="14"/>
+      <c r="B141" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C141" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="142" ht="34" spans="1:4">
+      <c r="A142" s="14"/>
+      <c r="B142" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="143" ht="17" spans="1:4">
+      <c r="A143" s="14"/>
+      <c r="B143" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C143" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="144" ht="34" spans="1:4">
+      <c r="A144" s="14"/>
+      <c r="B144" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C144" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="145" ht="34" spans="1:4">
+      <c r="A145" s="14"/>
+      <c r="B145" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C145" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="146" ht="34" spans="1:4">
+      <c r="A146" s="14"/>
+      <c r="B146" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="C146" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="147" ht="34" spans="1:4">
+      <c r="A147" s="14"/>
+      <c r="B147" s="31" t="s">
+        <v>401</v>
+      </c>
+      <c r="C147" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="148" ht="34" spans="1:4">
+      <c r="A148" s="14"/>
+      <c r="B148" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="C148" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="149" ht="84" spans="1:4">
+      <c r="A149" s="14"/>
+      <c r="B149" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C149" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="150" ht="84" spans="1:4">
+      <c r="A150" s="14"/>
+      <c r="B150" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="C150" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="151" ht="118" spans="1:4">
+      <c r="A151" s="14"/>
+      <c r="B151" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="C151" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="152" ht="34" spans="1:4">
+      <c r="A152" s="14"/>
+      <c r="B152" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="C152" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="153" ht="51" spans="1:4">
+      <c r="A153" s="14"/>
+      <c r="B153" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="154" ht="118" spans="1:4">
+      <c r="A154" s="14"/>
+      <c r="B154" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C154" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="155" ht="51" spans="1:4">
+      <c r="A155" s="15"/>
+      <c r="B155" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C155" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="156" ht="17" spans="1:4">
+      <c r="A156" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="C156" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="157" ht="17" spans="1:4">
+      <c r="A157" s="24"/>
+      <c r="B157" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C157" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="158" ht="51" spans="1:4">
+      <c r="A158" s="24"/>
+      <c r="B158" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="C158" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="24"/>
+      <c r="B159" s="12"/>
+      <c r="C159" s="21"/>
+      <c r="D159" s="5"/>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="24"/>
+      <c r="B160" s="25"/>
+      <c r="C160" s="26"/>
+      <c r="D160" s="5"/>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="24"/>
+      <c r="B161" s="25"/>
+      <c r="C161" s="26"/>
+      <c r="D161" s="5"/>
+    </row>
+    <row r="162" ht="17" spans="1:4">
+      <c r="A162" s="27" t="s">
+        <v>438</v>
+      </c>
+      <c r="B162" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="C162" s="26" t="s">
+        <v>440</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="163" ht="17" spans="1:4">
+      <c r="A163" s="27"/>
+      <c r="B163" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="C163" s="26" t="s">
+        <v>442</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="164" ht="17" spans="1:4">
+      <c r="A164" s="27"/>
+      <c r="B164" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="C164" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="165" ht="34" spans="1:4">
+      <c r="A165" s="27"/>
+      <c r="B165" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="C165" s="26" t="s">
+        <v>447</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="166" ht="17" spans="1:4">
+      <c r="A166" s="27"/>
+      <c r="B166" s="28" t="s">
+        <v>449</v>
+      </c>
+      <c r="C166" s="26" t="s">
+        <v>450</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="167" ht="17" spans="1:4">
+      <c r="A167" s="27"/>
+      <c r="B167" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="C167" s="26" t="s">
+        <v>453</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="168" ht="17" spans="1:4">
+      <c r="A168" s="27"/>
+      <c r="B168" s="29" t="s">
+        <v>455</v>
+      </c>
+      <c r="C168" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="169" ht="34" spans="1:4">
+      <c r="A169" s="27"/>
+      <c r="B169" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="C169" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="170" ht="34" spans="1:4">
+      <c r="A170" s="27"/>
+      <c r="B170" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="C170" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="171" ht="34" spans="1:4">
+      <c r="A171" s="27"/>
+      <c r="B171" s="28" t="s">
+        <v>464</v>
+      </c>
+      <c r="C171" s="26" t="s">
+        <v>465</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="172" ht="68" spans="1:4">
+      <c r="A172" s="27"/>
+      <c r="B172" s="28" t="s">
+        <v>467</v>
+      </c>
+      <c r="C172" s="26" t="s">
+        <v>468</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="173" ht="34" spans="1:4">
+      <c r="A173" s="27"/>
+      <c r="B173" s="28" t="s">
+        <v>470</v>
+      </c>
+      <c r="C173" s="26" t="s">
+        <v>471</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="27"/>
+      <c r="B174" s="28"/>
+      <c r="C174" s="26"/>
+      <c r="D174" s="5"/>
+    </row>
+    <row r="175" ht="17" spans="1:4">
+      <c r="A175" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="B175" s="28" t="s">
+        <v>473</v>
+      </c>
+      <c r="C175" s="26" t="s">
+        <v>474</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="176" ht="68" spans="1:4">
+      <c r="A176" s="27"/>
+      <c r="B176" s="28" t="s">
+        <v>476</v>
+      </c>
+      <c r="C176" s="26" t="s">
+        <v>477</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="177" ht="84" spans="1:4">
+      <c r="A177" s="27"/>
+      <c r="B177" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="C177" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="178" ht="84" spans="1:4">
+      <c r="A178" s="27"/>
+      <c r="B178" s="28" t="s">
+        <v>482</v>
+      </c>
+      <c r="C178" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="179" ht="84" spans="1:4">
+      <c r="A179" s="27"/>
+      <c r="B179" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="C179" s="26" t="s">
+        <v>486</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="180" ht="17" spans="1:4">
+      <c r="A180" s="27"/>
+      <c r="B180" s="28" t="s">
+        <v>488</v>
+      </c>
+      <c r="C180" s="26" t="s">
+        <v>489</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="27"/>
+      <c r="B181" s="28"/>
+      <c r="C181" s="26"/>
+      <c r="D181" s="5"/>
+    </row>
+    <row r="182" ht="17" spans="1:4">
+      <c r="A182" s="30" t="s">
+        <v>491</v>
+      </c>
+      <c r="B182" s="28" t="s">
+        <v>492</v>
+      </c>
+      <c r="C182" s="26" t="s">
+        <v>493</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="183" ht="17" spans="1:4">
+      <c r="A183" s="30"/>
+      <c r="B183" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C183" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="184" ht="17" spans="1:4">
+      <c r="A184" s="30"/>
+      <c r="B184" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="C184" s="26" t="s">
+        <v>498</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="185" ht="17" spans="1:4">
+      <c r="A185" s="30"/>
+      <c r="B185" s="28" t="s">
+        <v>500</v>
+      </c>
+      <c r="C185" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="186" ht="17" spans="1:4">
+      <c r="A186" s="30"/>
+      <c r="B186" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="C186" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="187" ht="17" spans="1:4">
+      <c r="A187" s="30"/>
+      <c r="B187" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="C187" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="188" ht="17" spans="1:4">
+      <c r="A188" s="30"/>
+      <c r="B188" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="C188" s="26" t="s">
+        <v>510</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="189" ht="34" spans="1:4">
+      <c r="A189" s="30"/>
+      <c r="B189" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="C189" s="26" t="s">
+        <v>513</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="190" ht="17" spans="1:4">
+      <c r="A190" s="30"/>
+      <c r="B190" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="C190" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="191" ht="17" spans="1:4">
+      <c r="A191" s="30"/>
+      <c r="B191" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="C191" s="26" t="s">
+        <v>519</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="192" ht="17" spans="1:4">
+      <c r="A192" s="30"/>
+      <c r="B192" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="C192" s="26" t="s">
+        <v>522</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="193" ht="17" spans="1:4">
+      <c r="A193" s="30"/>
+      <c r="B193" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="C193" s="26" t="s">
+        <v>525</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="194" ht="68" spans="1:4">
+      <c r="A194" s="30"/>
+      <c r="B194" s="28" t="s">
+        <v>527</v>
+      </c>
+      <c r="C194" s="26" t="s">
+        <v>528</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="30"/>
+      <c r="B195" s="28"/>
+      <c r="C195" s="26"/>
+      <c r="D195" s="5"/>
+    </row>
+    <row r="196" ht="34" spans="1:4">
+      <c r="A196" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="B196" s="28" t="s">
+        <v>531</v>
+      </c>
+      <c r="C196" s="26" t="s">
+        <v>532</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="197" ht="17" spans="1:4">
+      <c r="A197" s="30"/>
+      <c r="B197" s="28" t="s">
+        <v>534</v>
+      </c>
+      <c r="C197" s="26" t="s">
+        <v>535</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="198" ht="17" spans="1:4">
+      <c r="A198" s="30"/>
+      <c r="B198" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="C198" s="26" t="s">
+        <v>538</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="199" ht="51" spans="1:4">
+      <c r="A199" s="30"/>
+      <c r="B199" s="28" t="s">
+        <v>540</v>
+      </c>
+      <c r="C199" s="26" t="s">
+        <v>541</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="30"/>
+      <c r="B200" s="28"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="5"/>
+    </row>
+    <row r="201" ht="17" spans="1:4">
+      <c r="A201" s="30" t="s">
+        <v>543</v>
+      </c>
+      <c r="B201" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="C201" s="26" t="s">
+        <v>545</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="202" ht="17" spans="1:4">
+      <c r="A202" s="30"/>
+      <c r="B202" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="C202" s="26" t="s">
+        <v>548</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="203" ht="17" spans="1:4">
+      <c r="A203" s="30"/>
+      <c r="B203" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="C203" s="26" t="s">
+        <v>551</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="204" ht="17" spans="1:4">
+      <c r="A204" s="30"/>
+      <c r="B204" s="28" t="s">
+        <v>553</v>
+      </c>
+      <c r="C204" s="26" t="s">
+        <v>554</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="205" ht="17" spans="1:4">
+      <c r="A205" s="30"/>
+      <c r="B205" s="28" t="s">
+        <v>556</v>
+      </c>
+      <c r="C205" s="26" t="s">
+        <v>557</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="206" ht="34" spans="1:4">
+      <c r="A206" s="30"/>
+      <c r="B206" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="C206" s="26" t="s">
+        <v>559</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="207" ht="34" spans="1:4">
+      <c r="A207" s="30"/>
+      <c r="B207" s="28" t="s">
+        <v>561</v>
+      </c>
+      <c r="C207" s="26" t="s">
+        <v>562</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="30"/>
+      <c r="B208" s="28"/>
+      <c r="C208" s="26"/>
+      <c r="D208" s="5"/>
+    </row>
+    <row r="209" ht="17" spans="1:4">
+      <c r="A209" s="30" t="s">
+        <v>564</v>
+      </c>
+      <c r="B209" s="28" t="s">
+        <v>565</v>
+      </c>
+      <c r="C209" s="26" t="s">
+        <v>566</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="210" ht="68" spans="1:4">
+      <c r="A210" s="30"/>
+      <c r="B210" s="28" t="s">
+        <v>568</v>
+      </c>
+      <c r="C210" s="26" t="s">
+        <v>569</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="211" ht="34" spans="1:4">
+      <c r="A211" s="30"/>
+      <c r="B211" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="C211" s="26" t="s">
+        <v>572</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="212" ht="34" spans="1:4">
+      <c r="A212" s="30"/>
+      <c r="B212" s="28" t="s">
+        <v>574</v>
+      </c>
+      <c r="C212" s="26" t="s">
+        <v>575</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="213" ht="17" spans="1:4">
+      <c r="A213" s="30"/>
+      <c r="B213" s="28" t="s">
+        <v>577</v>
+      </c>
+      <c r="C213" s="26" t="s">
+        <v>578</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="214" ht="68" spans="1:4">
+      <c r="A214" s="30"/>
+      <c r="B214" s="28" t="s">
+        <v>580</v>
+      </c>
+      <c r="C214" s="26" t="s">
+        <v>581</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="215" ht="17" spans="1:4">
+      <c r="A215" s="30"/>
+      <c r="B215" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="C215" s="23" t="s">
+        <v>584</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="216" ht="84" spans="1:4">
+      <c r="A216" s="30"/>
+      <c r="B216" s="28" t="s">
+        <v>586</v>
+      </c>
+      <c r="C216" s="26" t="s">
+        <v>587</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="30"/>
+      <c r="B217" s="28"/>
+      <c r="C217" s="26"/>
+      <c r="D217" s="5"/>
+    </row>
+    <row r="218" ht="34" spans="1:4">
+      <c r="A218" s="30" t="s">
+        <v>589</v>
+      </c>
+      <c r="B218" s="28" t="s">
+        <v>590</v>
+      </c>
+      <c r="C218" s="26" t="s">
+        <v>591</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="219" ht="84" spans="1:4">
+      <c r="A219" s="30"/>
+      <c r="B219" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="C219" s="26" t="s">
+        <v>594</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="30"/>
+      <c r="B220" s="28"/>
+      <c r="C220" s="26"/>
+      <c r="D220" s="5"/>
+    </row>
+    <row r="221" ht="17" spans="1:4">
+      <c r="A221" s="30" t="s">
+        <v>596</v>
+      </c>
+      <c r="B221" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C221" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="222" ht="17" spans="1:4">
+      <c r="A222" s="30"/>
+      <c r="B222" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C222" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="223" ht="17" spans="1:4">
+      <c r="A223" s="30"/>
+      <c r="B223" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C223" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="224" ht="17" spans="1:4">
+      <c r="A224" s="30"/>
+      <c r="B224" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C224" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="225" ht="17" spans="1:4">
+      <c r="A225" s="30"/>
+      <c r="B225" s="28" t="s">
+        <v>597</v>
+      </c>
+      <c r="C225" s="26" t="s">
+        <v>598</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="226" ht="17" spans="1:4">
+      <c r="A226" s="30"/>
+      <c r="B226" s="28" t="s">
+        <v>600</v>
+      </c>
+      <c r="C226" s="26" t="s">
+        <v>601</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="227" ht="17" spans="1:4">
+      <c r="A227" s="30"/>
+      <c r="B227" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C227" s="26" t="s">
+        <v>604</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="228" ht="17" spans="1:4">
+      <c r="A228" s="30"/>
+      <c r="B228" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="C228" s="26" t="s">
+        <v>607</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="229" ht="17" spans="1:4">
+      <c r="A229" s="30"/>
+      <c r="B229" s="28" t="s">
+        <v>609</v>
+      </c>
+      <c r="C229" s="26" t="s">
+        <v>610</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="230" ht="17" spans="1:4">
+      <c r="A230" s="30"/>
+      <c r="B230" s="28" t="s">
+        <v>612</v>
+      </c>
+      <c r="C230" s="26" t="s">
+        <v>613</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="231" ht="17" spans="1:4">
+      <c r="A231" s="30"/>
+      <c r="B231" s="28" t="s">
+        <v>615</v>
+      </c>
+      <c r="C231" s="26" t="s">
+        <v>616</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="232" ht="17" spans="1:4">
+      <c r="A232" s="30"/>
+      <c r="B232" s="28" t="s">
+        <v>618</v>
+      </c>
+      <c r="C232" s="26" t="s">
+        <v>619</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="233" ht="17" spans="1:4">
+      <c r="A233" s="30"/>
+      <c r="B233" s="28" t="s">
+        <v>621</v>
+      </c>
+      <c r="C233" s="26" t="s">
+        <v>622</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="234" ht="17" spans="1:4">
+      <c r="A234" s="30"/>
+      <c r="B234" s="28" t="s">
+        <v>624</v>
+      </c>
+      <c r="C234" s="26" t="s">
+        <v>625</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="235" ht="17" spans="1:4">
+      <c r="A235" s="30"/>
+      <c r="B235" s="28" t="s">
+        <v>627</v>
+      </c>
+      <c r="C235" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="236" ht="17" spans="1:4">
+      <c r="A236" s="30"/>
+      <c r="B236" s="28" t="s">
+        <v>630</v>
+      </c>
+      <c r="C236" s="26" t="s">
+        <v>631</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="237" ht="17" spans="1:4">
+      <c r="A237" s="30"/>
+      <c r="B237" s="28" t="s">
+        <v>633</v>
+      </c>
+      <c r="C237" s="26" t="s">
+        <v>634</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="238" ht="17" spans="1:4">
+      <c r="A238" s="30"/>
+      <c r="B238" s="28" t="s">
+        <v>636</v>
+      </c>
+      <c r="C238" s="26" t="s">
+        <v>637</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="239" ht="17" spans="1:4">
+      <c r="A239" s="30"/>
+      <c r="B239" s="28" t="s">
+        <v>639</v>
+      </c>
+      <c r="C239" s="26" t="s">
+        <v>640</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="240" ht="17" spans="1:4">
+      <c r="A240" s="30"/>
+      <c r="B240" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="C240" s="26" t="s">
+        <v>643</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="241" ht="17" spans="1:4">
+      <c r="A241" s="30"/>
+      <c r="B241" s="28" t="s">
+        <v>645</v>
+      </c>
+      <c r="C241" s="26" t="s">
+        <v>646</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="242" ht="17" spans="1:4">
+      <c r="A242" s="30"/>
+      <c r="B242" s="28" t="s">
+        <v>648</v>
+      </c>
+      <c r="C242" s="26" t="s">
+        <v>649</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="243" ht="17" spans="1:4">
+      <c r="A243" s="30"/>
+      <c r="B243" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="C243" s="26" t="s">
+        <v>652</v>
+      </c>
+      <c r="D243" s="5" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="244" ht="17" spans="1:4">
+      <c r="A244" s="30"/>
+      <c r="B244" s="28" t="s">
+        <v>654</v>
+      </c>
+      <c r="C244" s="26" t="s">
+        <v>655</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="245" ht="17" spans="1:4">
+      <c r="A245" s="30"/>
+      <c r="B245" s="28" t="s">
+        <v>657</v>
+      </c>
+      <c r="C245" s="26" t="s">
+        <v>658</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="246" ht="17" spans="1:4">
+      <c r="A246" s="30"/>
+      <c r="B246" s="28" t="s">
+        <v>660</v>
+      </c>
+      <c r="C246" s="26" t="s">
+        <v>661</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="247" ht="17" spans="1:4">
+      <c r="A247" s="30"/>
+      <c r="B247" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="C247" s="26" t="s">
+        <v>664</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="248" ht="17" spans="1:4">
+      <c r="A248" s="30"/>
+      <c r="B248" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="C248" s="26" t="s">
+        <v>667</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="249" ht="17" spans="1:4">
+      <c r="A249" s="30"/>
+      <c r="B249" s="28" t="s">
+        <v>669</v>
+      </c>
+      <c r="C249" s="26" t="s">
+        <v>670</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="250" ht="17" spans="1:4">
+      <c r="A250" s="30"/>
+      <c r="B250" s="28" t="s">
+        <v>672</v>
+      </c>
+      <c r="C250" s="26" t="s">
+        <v>673</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="251" ht="17" spans="1:4">
+      <c r="A251" s="30"/>
+      <c r="B251" s="28" t="s">
+        <v>675</v>
+      </c>
+      <c r="C251" s="26" t="s">
+        <v>676</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="30"/>
+      <c r="B252" s="28"/>
+      <c r="C252" s="26"/>
+      <c r="D252" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="A45:A47"/>
+  <mergeCells count="20">
+    <mergeCell ref="A2:A53"/>
+    <mergeCell ref="A54:A62"/>
+    <mergeCell ref="A63:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A102"/>
+    <mergeCell ref="A103:A109"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="A114:A116"/>
+    <mergeCell ref="A117:A124"/>
+    <mergeCell ref="A125:A128"/>
+    <mergeCell ref="A129:A155"/>
+    <mergeCell ref="A156:A161"/>
+    <mergeCell ref="A162:A174"/>
+    <mergeCell ref="A175:A181"/>
+    <mergeCell ref="A182:A195"/>
+    <mergeCell ref="A196:A200"/>
+    <mergeCell ref="A201:A208"/>
+    <mergeCell ref="A209:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A221:A252"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/code/JieLi_Home_Demo/Languages/language.xlsx
+++ b/code/JieLi_Home_Demo/Languages/language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26160" windowHeight="16640"/>
+    <workbookView windowHeight="16640"/>
   </bookViews>
   <sheets>
     <sheet name="语言包" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="682">
   <si>
     <t>界面</t>
   </si>
@@ -2061,6 +2061,18 @@
   </si>
   <si>
     <t>ウルドゥー語</t>
+  </si>
+  <si>
+    <t>升级</t>
+  </si>
+  <si>
+    <t>无限制升级，但需要先将升级命名为：update.ufw 并通过沙盒，存放到：Document/ 目录下</t>
+  </si>
+  <si>
+    <t>Unlimited upgrades are available, but you must first name the upgrade file update.ufw, pass it through the sandbox, and save it to the Document/ directory.</t>
+  </si>
+  <si>
+    <t>アップグレードは無制限に可能ですが、まずアップグレードファイルをupdate.ufwと命名し、サンドボックスを通過させた上で **Document/** ディレクトリに保存してください。</t>
   </si>
 </sst>
 </file>
@@ -3497,7 +3509,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D252"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26.75" style="2" customWidth="1"/>
@@ -6440,6 +6452,20 @@
       <c r="B252" s="28"/>
       <c r="C252" s="26"/>
       <c r="D252" s="5"/>
+    </row>
+    <row r="253" ht="152" spans="1:4">
+      <c r="A253" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>681</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
